--- a/education_forms/045_wood_material_knowledge_quiz--education_forms.xlsx
+++ b/education_forms/045_wood_material_knowledge_quiz--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,15 +520,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>wood_material</t>
+          <t>wood_type</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wood Material</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What type of wood is commonly used for making furniture?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -538,20 +542,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>wood_type</t>
+          <t>wood_characteristics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wood Type</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Which wood is known for its durability and resistance to warping?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -561,20 +569,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>correct_answer</t>
+          <t>wood_density</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Correct Answer</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>What is the primary purpose of wood density?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -584,20 +596,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>correct_answer</t>
+          <t>wood_weight</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Correct Answer</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What is the average weight of a standard piece of wood?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -607,20 +623,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>wood_density</t>
+          <t>wood_type_floors</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wood Density</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What type of wood is often used for flooring?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -635,15 +655,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>wood_weight</t>
+          <t>wood_description</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wood Weight</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>How would you describe the color of this wood?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -653,20 +677,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>correct_answer</t>
+          <t>wood_engineered</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Correct Answer</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>What is the primary difference between Solid Wood and Engineered Wood?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -676,20 +704,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>correct_answer</t>
+          <t>mdf_purpose</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Correct Answer</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>What is the purpose of MDF?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -699,20 +731,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>correct_answer</t>
+          <t>teak_benefit</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Correct Answer</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>What is the primary benefit of using Teak wood?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -727,15 +763,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>correct_answer</t>
+          <t>correct_answer_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Correct Answer</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>What is the correct answer to the question above?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -750,15 +790,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>correct_answer</t>
+          <t>correct_answer_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Correct Answer</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>What is the correct answer to this question?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -773,15 +817,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>correct_answer</t>
+          <t>correct_answer_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Correct Answer</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Correct Answer 3</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -796,15 +844,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>correct_answer</t>
+          <t>correct_answer_4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Correct Answer</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Correct Answer 4</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -819,269 +871,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>correct_answer</t>
+          <t>correct_answer_5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Correct Answer</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Correct Answer 5</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>correct_answer</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Correct Answer</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>correct_answer</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Correct Answer</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>correct_answer</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Correct Answer</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>correct_answer</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Correct Answer</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>correct_answer</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Correct Answer</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>correct_answer</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Correct Answer</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>correct_answer</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Correct Answer</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>correct_answer</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Correct Answer</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>correct_answer</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Correct Answer</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>correct_answer</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Correct Answer</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>correct_answer</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Correct Answer</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +901,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,7 +929,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>wood_material_choices</t>
+          <t>wood_type_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +946,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>wood_material_choices</t>
+          <t>wood_type_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,7 +963,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>wood_material_choices</t>
+          <t>wood_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,867 +980,425 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>wood_material_choices</t>
+          <t>wood_type_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>birch</t>
+          <t>cherry</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Birch</t>
+          <t>Cherry</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>wood_material_choices</t>
+          <t>wood_type_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>cherry</t>
+          <t>walnut</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cherry</t>
+          <t>Walnut</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>wood_material_choices</t>
+          <t>wood_type_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>walnut</t>
+          <t>ash</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Walnut</t>
+          <t>Ash</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>wood_material_choices</t>
+          <t>wood_characteristics_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ash</t>
+          <t>teak</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ash</t>
+          <t>Teak</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>wood_material_choices</t>
+          <t>wood_characteristics_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>beech</t>
+          <t>oak</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Beech</t>
+          <t>Oak</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>wood_material_choices</t>
+          <t>wood_characteristics_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>teak</t>
+          <t>pine</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Teak</t>
+          <t>Pine</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>wood_type_choices</t>
+          <t>wood_characteristics_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>solid_wood</t>
+          <t>maple</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Solid Wood</t>
+          <t>Maple</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>wood_type_choices</t>
+          <t>wood_characteristics_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>engineered_wood</t>
+          <t>cherry</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Engineered Wood</t>
+          <t>Cherry</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>wood_type_choices</t>
+          <t>wood_characteristics_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>plywood</t>
+          <t>ash</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plywood</t>
+          <t>Ash</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>wood_type_choices</t>
+          <t>wood_type_floors_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>mdf</t>
+          <t>oak</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDF</t>
+          <t>Oak</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>wood_type_choices</t>
+          <t>wood_type_floors_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>particleboard</t>
+          <t>maple</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Particleboard</t>
+          <t>Maple</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>wood_type_choices</t>
+          <t>wood_type_floors_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>moulding</t>
+          <t>pine</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Moulding</t>
+          <t>Pine</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>correct_answer_choices</t>
+          <t>wood_type_floors_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>cherry</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Cherry</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>correct_answer_choices</t>
+          <t>wood_type_floors_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>walnut</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Walnut</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>correct_answer_choices</t>
+          <t>wood_type_floors_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>ash</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Ash</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>correct_answer_choices</t>
+          <t>correct_answer_1_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>correct_answer_choices</t>
+          <t>correct_answer_1_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>correct_answer_choices</t>
+          <t>correct_answer_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>correct_answer_choices</t>
+          <t>correct_answer_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>correct_answer_choices</t>
+          <t>correct_answer_3_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>correct_answer_choices</t>
+          <t>correct_answer_3_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>correct_answer_choices</t>
+          <t>correct_answer_4_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>correct_answer_choices</t>
+          <t>correct_answer_4_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>correct_answer_choices</t>
+          <t>correct_answer_5_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>correct_answer_choices</t>
+          <t>correct_answer_5_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>correct_answer_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>reported</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>reported</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>correct_answer_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>correct_answer_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>reported</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>reported</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>correct_answer_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>correct_answer_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>reported</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>reported</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>correct_answer_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>correct_answer_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>reported</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>reported</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>correct_answer_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>correct_answer_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>reported</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>reported</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>correct_answer_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>correct_answer_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>reported</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>reported</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>correct_answer_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>correct_answer_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>reported</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>reported</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>correct_answer_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>correct_answer_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>reported</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>reported</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>correct_answer_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>correct_answer_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>reported</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>reported</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>correct_answer_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>correct_answer_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>reported</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>reported</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>correct_answer_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>correct_answer_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>reported</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>reported</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>correct_answer_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>correct_answer_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>reported</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>reported</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>correct_answer_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>correct_answer_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>reported</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>reported</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>correct_answer_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Other</t>
+          <t>False</t>
         </is>
       </c>
     </row>
